--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-21.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_2B59D187544A3A6C1BB83811598B00365E0FE921" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEF602A-A1F0-4B83-A6CD-4195D214E6D5}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_2B59D187544A3A6C1BB83811598B00365E0FE921" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641950CC-8CC6-43E3-A3EE-A053ADFD11AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="47">
   <si>
     <t>Data</t>
   </si>
@@ -158,9 +158,6 @@
     <t>ITALY 3</t>
   </si>
   <si>
-    <t>SSD Bari x Cavese 1919</t>
-  </si>
-  <si>
     <t>Union Brescia x Carpi</t>
   </si>
   <si>
@@ -171,15 +168,6 @@
   </si>
   <si>
     <t>The Strongest x Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>COLOMBIA 1</t>
-  </si>
-  <si>
-    <t>Alianza FC Valledupar x Deportivo Pereira</t>
   </si>
   <si>
     <t>1/0</t>
@@ -566,9 +554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
     <col min="5" max="5" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -607,10 +596,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -693,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M13" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
+        <f t="shared" ref="M3:M11" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
         <v>0.21636771300448429</v>
       </c>
     </row>
@@ -930,10 +919,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>9.24</v>
+        <v>12.6</v>
       </c>
       <c r="I9">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -946,7 +935,7 @@
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.11711165048543688</v>
+        <v>8.3189655172413793E-2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -960,35 +949,35 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10">
-        <v>12.6</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="I10">
         <v>1.36</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
-        <v>8.3189655172413793E-2</v>
+        <v>0.24492385786802026</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -996,13 +985,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1014,10 +1003,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>4.9400000000000004</v>
+        <v>5.46</v>
       </c>
       <c r="I11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
@@ -1030,91 +1019,7 @@
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>0.24492385786802026</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12">
-        <v>5.46</v>
-      </c>
-      <c r="I12">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="0"/>
         <v>0.21636771300448429</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13">
-        <v>10.5</v>
-      </c>
-      <c r="I13">
-        <v>1.58</v>
-      </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="0"/>
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
